--- a/SampleExcel.xlsx
+++ b/SampleExcel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Kerja\Codes\eFilingExcel\eFilingExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27FDBA31-DCD3-476B-858F-C52D99793ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E8B1063-C30B-41FC-BFF6-9A6DE702AA15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="49080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ECFA7F17-5E05-46F9-9D5D-5601CC2FFC56}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -120,13 +120,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -461,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE47C67E-7212-47C9-98D7-765F3F18A8CF}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -470,13 +469,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -502,7 +501,7 @@
       <c r="B3">
         <v>1234</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="1">
         <v>29838</v>
       </c>
       <c r="D3" t="s">
@@ -519,8 +518,8 @@
       <c r="B4">
         <v>12121</v>
       </c>
-      <c r="C4" s="2">
-        <v>36526</v>
+      <c r="C4" s="1">
+        <v>37144</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -528,6 +527,90 @@
       <c r="E4">
         <v>111</v>
       </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="1"/>
     </row>
   </sheetData>
   <dataConsolidate/>
